--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A72381D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1100,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq35，推进7站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1141,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2370,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2420,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2481,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2531,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2592,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2642,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2703,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2753,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2814,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2864,1010 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A57091D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A69930D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A62773D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq35，推进7站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1371,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1482,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1593,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1704,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1815,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1926,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2378,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2592,7 +2600,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2703,7 +2711,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2822,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,7 +2933,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3044,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3147,7 +3155,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3258,7 +3266,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3369,7 +3377,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3480,7 +3488,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3591,7 +3599,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3702,7 +3710,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3813,7 +3821,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3862,12 +3870,242 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -892,12 +892,12 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1235,32 +1235,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1268,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,33 +1296,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1346,32 +1354,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1379,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,33 +1415,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1473,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1490,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,33 +1534,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1568,32 +1592,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1601,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,33 +1653,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1751,7 +1783,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1823,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,12 +1933,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1934,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,10 +1974,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2045,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2234,12 +2282,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq47，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2267,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2275,10 +2323,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq38（站名待映射） ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2378,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3108,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3155,7 +3219,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,7 +3330,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3377,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3488,7 +3552,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3599,7 +3663,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3710,7 +3774,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3821,7 +3885,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3870,7 +3934,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -3936,7 +4000,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4008,7 +4072,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4051,7 +4115,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4065,47 +4129,844 @@
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>156.0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr">
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1711,32 +1711,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1744,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,17 +1772,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1788,13 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1822,32 +1830,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1855,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,33 +1891,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1954,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1966,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2060,32 +2076,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2093,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,33 +2137,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2171,32 +2195,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2204,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2228,33 +2256,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2319,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq47，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq61，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2315,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2513,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2520,32 +2552,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2553,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2577,33 +2613,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2703,7 +2743,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2775,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2854,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2886,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,7 +2965,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2997,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3108,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3330,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3703,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,7 +3814,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3925,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,7 +4040,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,7 +4155,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4169,7 +4209,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4270,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4385,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4456,7 +4496,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4510,7 +4550,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4611,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4625,7 +4665,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4726,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4801,7 +4841,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4855,7 +4895,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4956,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4960,11 +5000,1030 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A72381D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr"/>
-      <c r="AC39" s="2" t="inlineStr">
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
         </is>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3004,32 +3004,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3061,17 +3065,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3081,13 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3115,32 +3123,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3148,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3172,17 +3184,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3192,13 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,7 +3314,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3370,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3481,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,7 +3536,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3592,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3631,7 +3647,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3703,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3781,32 +3797,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3814,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3838,33 +3858,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3892,32 +3916,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3925,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3949,17 +3977,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3969,17 +3997,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4194,7 +4222,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4209,7 +4237,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4237,32 +4265,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4270,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4294,37 +4326,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4384,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4385,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4393,10 +4425,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4496,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4550,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4578,32 +4626,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4611,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4635,17 +4687,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4655,17 +4707,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4780,7 +4832,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4880,7 +4932,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4895,7 +4947,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4956,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5010,7 +5062,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5125,7 +5177,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5238,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5240,7 +5292,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5353,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5355,7 +5407,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5468,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5470,7 +5522,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5583,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5642,7 +5694,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5753,7 +5805,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5864,7 +5916,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5975,7 +6027,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6019,13 +6071,810 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr"/>
-      <c r="AC48" s="2" t="inlineStr">
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A69930D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2152,22 +2152,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2518,13 +2518,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2633,17 +2637,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2747,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2754,7 +2758,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2865,7 +2869,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2980,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3329,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3440,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3547,7 +3551,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3658,7 +3662,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3773,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3888,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4011,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4126,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4237,7 +4241,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4356,7 +4360,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4393,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4417,7 +4421,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4483,7 +4487,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4511,32 +4515,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4544,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4568,17 +4576,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4588,17 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4636,12 +4644,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -4663,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4712,12 +4720,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4817,7 +4825,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4832,7 +4840,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4860,32 +4868,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4893,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4917,17 +4929,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4937,17 +4949,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4975,32 +4987,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5008,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5032,17 +5048,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5052,17 +5068,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5177,7 +5193,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5292,7 +5308,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5320,32 +5336,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5353,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5377,37 +5397,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5435,32 +5455,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5468,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5492,17 +5516,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5512,17 +5536,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5550,32 +5574,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5583,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5607,17 +5635,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5627,13 +5655,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5726,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5744,7 +5776,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5844,7 +5876,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5855,7 +5887,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5948,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5966,7 +5998,7 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6081,7 +6113,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6174,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6192,7 +6224,7 @@
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6285,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6303,7 +6335,7 @@
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6396,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6414,7 +6446,7 @@
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6507,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6529,7 +6561,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6622,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6644,7 +6676,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6737,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6759,7 +6791,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6852,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6864,17 +6896,691 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>11/28</t>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,14 +2632,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2752,13 +2752,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,18 +2862,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,13 +2982,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,22 +3096,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,18 +3330,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,13 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3838,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4011,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4241,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4360,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4840,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4959,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5193,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5427,7 +5447,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5531,14 +5551,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -5546,7 +5566,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5693,32 +5713,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5726,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5750,33 +5774,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5804,32 +5832,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5837,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5861,17 +5893,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5881,13 +5913,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5915,32 +5951,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5948,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5972,17 +6012,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -5992,13 +6032,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6026,32 +6070,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6059,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6083,37 +6131,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6141,32 +6189,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6174,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6198,33 +6250,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6252,32 +6308,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6285,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6309,17 +6369,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6329,13 +6389,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6435,7 +6499,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6507,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6622,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6676,7 +6740,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6791,7 +6855,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6916,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6906,7 +6970,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6967,7 +7031,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7021,7 +7085,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7146,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7193,7 +7257,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7304,7 +7368,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7358,7 +7422,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7483,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7530,7 +7594,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7574,13 +7638,588 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr"/>
-      <c r="AC61" s="2" t="inlineStr">
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
         <is>
           <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>138.5</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,13 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3902,7 +3906,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3977,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,14 +4020,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>138.5</t>
@@ -4031,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4246,22 +4250,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4380,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4860,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4979,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5447,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5566,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5869,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5923,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6161,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6427,32 +6431,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6460,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6484,17 +6492,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6504,13 +6512,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6538,32 +6550,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6571,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6595,17 +6611,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6615,7 +6631,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6653,32 +6669,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6686,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6710,37 +6730,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6855,7 +6875,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6970,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7085,7 +7105,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7166,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7257,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,7 +7388,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7422,7 +7442,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7503,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,7 +7614,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7648,7 +7668,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7729,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7763,7 +7783,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7844,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7939,7 +7959,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7993,7 +8013,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8074,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8098,13 +8118,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8165,7 +8189,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8223,6 +8247,236 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,14 +1430,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>151.5</t>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,22 +1668,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,18 +2037,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2593,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2647,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2762,7 +2766,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2992,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3345,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,12 +4264,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,17 +4378,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,14 +4619,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>151.5</t>
@@ -4630,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,22 +4972,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5202,7 +5206,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5217,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5451,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5570,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5873,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6165,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6284,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6679,24 +6683,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6706,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6755,12 +6759,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6788,32 +6792,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6821,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,17 +6853,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6865,17 +6873,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6903,32 +6911,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6936,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6960,37 +6972,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7018,32 +7030,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7051,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7075,17 +7091,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7095,17 +7111,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7133,12 +7149,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7166,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7174,10 +7190,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7244,32 +7276,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7277,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7301,33 +7337,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7442,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7614,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7668,7 +7708,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7783,7 +7823,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7898,7 +7938,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8013,7 +8053,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8114,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8128,7 +8168,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8189,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8304,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8353,12 +8393,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8459,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8473,7 +8513,467 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>151.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2161,17 +2161,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2411,13 +2411,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2601,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2641,17 +2645,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2756,17 +2760,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2881,7 +2885,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3115,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,14 +3223,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>149.0</t>
@@ -3234,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3339,17 +3343,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3464,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3690,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3805,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4039,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,7 +4508,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4515,7 +4519,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4634,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4867,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4987,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5221,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,7 +5325,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5336,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,17 +5449,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,17 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5812,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,17 +5925,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6169,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,17 +6282,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6764,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7040,24 +7044,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7067,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7116,12 +7120,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7158,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7182,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7248,7 +7252,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7367,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7395,32 +7399,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7428,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,17 +7460,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7472,17 +7480,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7510,32 +7518,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7543,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7567,17 +7579,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7587,13 +7599,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7621,32 +7637,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7654,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7678,17 +7698,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7698,17 +7718,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7736,32 +7756,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7769,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7793,17 +7817,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7813,17 +7837,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7851,32 +7875,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7884,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7908,17 +7936,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7928,17 +7956,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7999,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8053,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8168,7 +8196,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8283,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8398,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8513,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8628,7 +8656,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8743,7 +8771,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8858,7 +8886,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8973,7 +9001,459 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A57091D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,14 +1787,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2870,22 +2870,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,14 +4377,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,14 +5095,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,22 +5801,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6520,17 +6520,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6872,14 +6872,14 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7766,24 +7766,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7885,24 +7885,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7994,32 +7994,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8027,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,17 +8055,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8071,12 +8075,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8109,32 +8113,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8142,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8166,17 +8174,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8186,17 +8194,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8224,32 +8232,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8257,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,37 +8293,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8339,32 +8351,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8372,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8396,17 +8412,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8416,17 +8432,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8602,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8717,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8832,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8947,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9062,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9173,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9284,7 +9300,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9346,22 +9362,22 @@
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9394,12 +9410,12 @@
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9448,12 +9464,1047 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
           <t>164.0</t>
         </is>
       </c>
-      <c r="AC76" s="2" t="inlineStr">
+      <c r="AC77" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A69930D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6996,17 +6996,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7361,17 +7361,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8123,24 +8123,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8470,32 +8470,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8503,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8527,37 +8531,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8585,32 +8589,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8618,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8642,17 +8650,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8662,17 +8670,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8772,7 +8780,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8815,32 +8823,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8848,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8872,17 +8884,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8892,17 +8904,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8930,32 +8942,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8963,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8987,17 +9003,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9007,12 +9023,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9045,12 +9061,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq45，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9078,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9086,10 +9102,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="2" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -9300,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9415,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9469,7 +9501,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9645,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9760,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9875,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9990,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10105,7 +10137,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10159,7 +10191,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10252,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10335,7 +10367,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10450,7 +10482,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10504,7 +10536,697 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A72381D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>151.5</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2640,14 +2640,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>141.3</t>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,22 +4143,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,17 +4628,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,14 +5563,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>141.3</t>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,22 +6396,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7599,17 +7599,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,14 +7832,14 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>141.3</t>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -8708,32 +8708,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8741,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8765,17 +8769,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8785,17 +8789,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8899,7 +8903,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8914,7 +8918,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8956,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -8979,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9028,12 +9032,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9070,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq45，推进17站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9094,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9160,7 +9164,7 @@
       <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9275,7 @@
       <c r="AB74" s="2" t="inlineStr"/>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9299,32 +9303,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9332,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9356,37 +9364,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -9414,32 +9422,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9447,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9471,17 +9483,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9491,17 +9503,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9529,32 +9541,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9562,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9586,17 +9602,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9606,17 +9622,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9644,32 +9660,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9677,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9701,37 +9721,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -9759,32 +9779,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9792,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9816,37 +9840,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -9907,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9961,7 +9985,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10076,7 +10100,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10191,7 +10215,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10306,7 +10330,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10421,7 +10445,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -10482,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10536,7 +10560,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10651,7 +10675,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10736,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10766,7 +10790,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -10827,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10881,7 +10905,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -10942,7 +10966,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10996,7 +11020,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11057,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11101,17 +11125,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11196,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11226,7 +11250,808 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>4/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>8/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A57091D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>21/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>—/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>19/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A69930D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>14/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>9/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,22 +1311,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,22 +6634,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6877,17 +6877,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7115,17 +7115,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8313,17 +8313,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9670,24 +9670,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -9898,32 +9898,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9931,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,37 +9959,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -10013,32 +10017,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10046,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10070,37 +10078,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10128,32 +10136,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10161,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10185,17 +10197,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10205,17 +10217,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10243,32 +10255,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10276,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,17 +10316,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10320,17 +10336,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -10358,32 +10374,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10391,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10415,17 +10435,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10435,17 +10455,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10473,32 +10493,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -10506,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10530,17 +10554,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10550,17 +10574,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10675,7 +10699,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10851,7 +10875,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10905,7 +10929,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11020,7 +11044,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11196,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11250,7 +11274,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11365,7 +11389,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11480,7 +11504,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11595,7 +11619,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11680,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11767,7 +11791,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11821,7 +11845,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11906,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11936,7 +11960,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -11997,7 +12021,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12046,12 +12070,587 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>7/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>153.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>25/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>134.3</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>5/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>19/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>142.3</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>18/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>24/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>151.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2161,17 +2161,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2521,22 +2521,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3228,17 +3228,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3343,17 +3343,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,17 +4628,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>151.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5449,17 +5449,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,22 +5682,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6282,17 +6282,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7480,17 +7480,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7718,17 +7718,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7956,17 +7956,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8551,17 +8551,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8789,17 +8789,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>151.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10503,12 +10503,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -10612,32 +10612,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10645,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10669,17 +10673,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10689,17 +10693,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -10727,32 +10731,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10760,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10784,37 +10792,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -10842,32 +10850,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10875,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10899,17 +10911,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10919,17 +10931,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -10957,32 +10969,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10990,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11014,17 +11030,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11034,17 +11050,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11072,32 +11088,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11105,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11129,17 +11149,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11149,17 +11169,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>151.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -11187,32 +11207,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11220,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11244,17 +11268,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11264,17 +11288,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -11335,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11389,7 +11413,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11489,7 +11513,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11504,7 +11528,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -11532,32 +11556,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11565,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11589,17 +11617,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11609,17 +11637,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11680,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11791,7 +11819,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11845,7 +11873,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -11873,12 +11901,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq29推进至seq35，推进6站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -11906,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11914,10 +11942,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q97" s="2" t="inlineStr"/>
-      <c r="R97" s="2" t="inlineStr"/>
-      <c r="S97" s="2" t="inlineStr"/>
-      <c r="T97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
           <t>19:00</t>
@@ -11960,7 +12004,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12065,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12075,7 +12119,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -12136,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12251,7 +12295,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12305,7 +12349,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12410,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12420,7 +12464,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12525,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12535,7 +12579,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -12596,7 +12640,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12650,7 +12694,467 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>21/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>145.3</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>22/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A72381D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>4/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>3/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2645,17 +2645,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7837,17 +7837,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9741,17 +9741,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -11566,12 +11566,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -11675,32 +11675,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>18:01</t>
@@ -11708,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11732,17 +11736,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11752,13 +11756,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB95" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -11786,32 +11794,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11819,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11843,17 +11855,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11863,17 +11875,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11918,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq29推进至seq35，推进6站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -11934,7 +11946,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12004,7 +12016,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -12032,32 +12044,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12065,7 +12081,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12089,17 +12105,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12109,17 +12125,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -12147,32 +12163,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12180,7 +12200,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12204,17 +12224,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12224,12 +12244,12 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12262,12 +12282,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12295,7 +12315,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12303,10 +12323,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:20</t>
@@ -12349,7 +12385,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12446,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12464,7 +12500,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12561,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12579,7 +12615,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -12607,32 +12643,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12640,7 +12680,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12664,17 +12704,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12684,12 +12724,12 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
@@ -12755,7 +12795,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12809,7 +12849,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -12870,7 +12910,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12924,7 +12964,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -12985,7 +13025,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13039,7 +13079,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -13100,7 +13140,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13154,7 +13194,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-16-浦东35路.xlsx
+++ b/data/export/2026-10-16-浦东35路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3109,17 +3109,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8075,17 +8075,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9627,12 +9627,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10098,17 +10098,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10336,17 +10336,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -12528,32 +12528,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12561,7 +12565,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12585,17 +12589,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12605,17 +12609,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -12653,24 +12657,24 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12680,7 +12684,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12729,12 +12733,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -12762,32 +12766,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12795,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12819,17 +12827,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12839,17 +12847,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -12877,32 +12885,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12910,7 +12922,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12934,17 +12946,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12954,17 +12966,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -13025,7 +13037,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13140,7 +13152,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
